--- a/my_stocks.xlsx
+++ b/my_stocks.xlsx
@@ -1,187 +1,249 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="10575" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="23040" windowHeight="10575"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>stocks</t>
+  </si>
+  <si>
+    <t>start_date</t>
+  </si>
+  <si>
+    <t>end_date</t>
+  </si>
+  <si>
+    <t>t_start_date</t>
+  </si>
+  <si>
+    <t>t_end_date</t>
+  </si>
+  <si>
+    <t>enable</t>
+  </si>
+  <si>
+    <t>神火股份</t>
+  </si>
+  <si>
+    <t>云铝股份</t>
+  </si>
+  <si>
+    <t>云天化</t>
+  </si>
+  <si>
+    <t>珀莱雅</t>
+  </si>
+  <si>
+    <t>紫金矿业</t>
+  </si>
+  <si>
+    <t>台基股份</t>
+  </si>
+  <si>
+    <t>深圳华强</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="21">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="14"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -481,174 +543,167 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -702,74 +757,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1021,184 +1013,216 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col width="26.9557522123894" customWidth="1" style="2" min="1" max="1"/>
-    <col width="16.7345132743363" customWidth="1" style="2" min="2" max="2"/>
-    <col width="15.3362831858407" customWidth="1" style="2" min="3" max="3"/>
-    <col width="27.2212389380531" customWidth="1" style="2" min="4" max="4"/>
-    <col width="18.858407079646" customWidth="1" style="2" min="5" max="5"/>
+    <col min="1" max="1" width="26.9557522123894" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7345132743363" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3362831858407" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.2212389380531" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.858407079646" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.6" customHeight="1" s="6">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>stocks</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>start_date</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>end_date</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>t_start_date</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>t_end_date</t>
-        </is>
-      </c>
-      <c r="F1" s="0" t="inlineStr">
-        <is>
-          <t>enable</t>
-        </is>
+    <row r="1" ht="17.6" customHeight="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1" s="6">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>神火股份</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="n">
+    <row r="2" ht="22" customHeight="1" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3">
         <v>43831</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="3">
         <v>46164</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="3">
         <v>45292</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="3">
         <v>46163</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3">
+        <v>43831</v>
+      </c>
+      <c r="C3" s="3">
+        <v>46164</v>
+      </c>
+      <c r="D3" s="3">
+        <v>45292</v>
+      </c>
+      <c r="E3" s="3">
+        <v>46163</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3">
+        <v>43831</v>
+      </c>
+      <c r="C4" s="3">
+        <v>46164</v>
+      </c>
+      <c r="D4" s="3">
+        <v>45292</v>
+      </c>
+      <c r="E4" s="3">
+        <v>46163</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3">
+        <v>43831</v>
+      </c>
+      <c r="C5" s="3">
+        <v>46164</v>
+      </c>
+      <c r="D5" s="3">
+        <v>45292</v>
+      </c>
+      <c r="E5" s="3">
+        <v>46163</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="3">
+        <v>43831</v>
+      </c>
+      <c r="C6" s="3">
+        <v>46164</v>
+      </c>
+      <c r="D6" s="3">
+        <v>45292</v>
+      </c>
+      <c r="E6" s="3">
+        <v>46163</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3">
+        <v>43831</v>
+      </c>
+      <c r="C7" s="3">
+        <v>46164</v>
+      </c>
+      <c r="D7" s="3">
+        <v>45292</v>
+      </c>
+      <c r="E7" s="3">
+        <v>46163</v>
+      </c>
+      <c r="F7" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1" s="6">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>云铝股份</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
+    <row r="8" ht="18" customHeight="1" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="3">
         <v>43831</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C8" s="3">
         <v>46164</v>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D8" s="3">
         <v>45292</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E8" s="3">
         <v>46163</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="F8" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" s="6">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>云天化</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>43831</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>46164</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>45292</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>46163</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" s="6">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>珀莱雅</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>43831</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>46164</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>45292</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>46163</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" s="6"/>
-    <row r="7" ht="18" customHeight="1" s="6"/>
-    <row r="8" ht="18" customHeight="1" s="6"/>
-    <row r="9" ht="18" customHeight="1" s="6"/>
-    <row r="10" ht="18" customHeight="1" s="6"/>
-    <row r="11" ht="18" customHeight="1" s="6"/>
-    <row r="12" ht="18" customHeight="1" s="6"/>
-    <row r="13" ht="18" customHeight="1" s="6"/>
-    <row r="14" ht="18" customHeight="1" s="6"/>
-    <row r="15" ht="18" customHeight="1" s="6"/>
-    <row r="16" ht="18" customHeight="1" s="6"/>
-    <row r="17" ht="18" customHeight="1" s="6"/>
-    <row r="18" ht="18" customHeight="1" s="6"/>
+    <row r="9" ht="18" customHeight="1"/>
+    <row r="10" ht="18" customHeight="1"/>
+    <row r="11" ht="18" customHeight="1"/>
+    <row r="12" ht="18" customHeight="1"/>
+    <row r="13" ht="18" customHeight="1"/>
+    <row r="14" ht="18" customHeight="1"/>
+    <row r="15" ht="18" customHeight="1"/>
+    <row r="16" ht="18" customHeight="1"/>
+    <row r="17" ht="18" customHeight="1"/>
+    <row r="18" ht="18" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/my_stocks.xlsx
+++ b/my_stocks.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>stocks</t>
   </si>
@@ -68,6 +68,18 @@
   </si>
   <si>
     <t>深圳华强</t>
+  </si>
+  <si>
+    <t>兆易创新</t>
+  </si>
+  <si>
+    <t>沪电股份</t>
+  </si>
+  <si>
+    <t>立讯精密</t>
+  </si>
+  <si>
+    <t>长电科技</t>
   </si>
 </sst>
 </file>
@@ -1060,10 +1072,10 @@
         <v>45292</v>
       </c>
       <c r="E2" s="3">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6">
@@ -1080,7 +1092,7 @@
         <v>45292</v>
       </c>
       <c r="E3" s="3">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -1100,7 +1112,7 @@
         <v>45292</v>
       </c>
       <c r="E4" s="3">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1120,7 +1132,7 @@
         <v>45292</v>
       </c>
       <c r="E5" s="3">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1140,7 +1152,7 @@
         <v>45292</v>
       </c>
       <c r="E6" s="3">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1160,10 +1172,10 @@
         <v>45292</v>
       </c>
       <c r="E7" s="3">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:6">
@@ -1180,17 +1192,98 @@
         <v>45292</v>
       </c>
       <c r="E8" s="3">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1"/>
-    <row r="10" ht="18" customHeight="1"/>
-    <row r="11" ht="18" customHeight="1"/>
-    <row r="12" ht="18" customHeight="1"/>
-    <row r="13" ht="18" customHeight="1"/>
+    <row r="9" ht="18" customHeight="1" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3">
+        <v>43831</v>
+      </c>
+      <c r="C9" s="3">
+        <v>46164</v>
+      </c>
+      <c r="D9" s="3">
+        <v>45292</v>
+      </c>
+      <c r="E9" s="3">
+        <v>46164</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3">
+        <v>43831</v>
+      </c>
+      <c r="C10" s="3">
+        <v>46164</v>
+      </c>
+      <c r="D10" s="3">
+        <v>45292</v>
+      </c>
+      <c r="E10" s="3">
+        <v>46164</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="3">
+        <v>43831</v>
+      </c>
+      <c r="C11" s="3">
+        <v>46164</v>
+      </c>
+      <c r="D11" s="3">
+        <v>45292</v>
+      </c>
+      <c r="E11" s="3">
+        <v>46164</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:6">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="3">
+        <v>43831</v>
+      </c>
+      <c r="C12" s="3">
+        <v>46164</v>
+      </c>
+      <c r="D12" s="3">
+        <v>45292</v>
+      </c>
+      <c r="E12" s="3">
+        <v>46164</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:6">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
     <row r="14" ht="18" customHeight="1"/>
     <row r="15" ht="18" customHeight="1"/>
     <row r="16" ht="18" customHeight="1"/>

--- a/my_stocks.xlsx
+++ b/my_stocks.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>stocks</t>
   </si>
@@ -80,6 +80,12 @@
   </si>
   <si>
     <t>长电科技</t>
+  </si>
+  <si>
+    <t>赛轮轮胎</t>
+  </si>
+  <si>
+    <t>神农股份</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1081,7 @@
         <v>46164</v>
       </c>
       <c r="F2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6">
@@ -1279,12 +1285,45 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:6">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="A13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="3">
+        <v>43831</v>
+      </c>
+      <c r="C13" s="3">
+        <v>46164</v>
+      </c>
+      <c r="D13" s="3">
+        <v>45292</v>
+      </c>
+      <c r="E13" s="3">
+        <v>46164</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" ht="18" customHeight="1"/>
+    <row r="14" ht="18" customHeight="1" spans="1:6">
+      <c r="A14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="3">
+        <v>43831</v>
+      </c>
+      <c r="C14" s="3">
+        <v>46164</v>
+      </c>
+      <c r="D14" s="3">
+        <v>45292</v>
+      </c>
+      <c r="E14" s="3">
+        <v>46164</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+    </row>
     <row r="15" ht="18" customHeight="1"/>
     <row r="16" ht="18" customHeight="1"/>
     <row r="17" ht="18" customHeight="1"/>

--- a/my_stocks.xlsx
+++ b/my_stocks.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10575"/>
+    <workbookView windowWidth="32065" windowHeight="14605"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1034,13 +1034,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="26.9557522123894" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7345132743363" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.3362831858407" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.2212389380531" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.858407079646" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.954954954955" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7387387387387" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.2252252252252" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.8558558558559" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1081,7 +1081,7 @@
         <v>46164</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6">
@@ -1301,7 +1301,7 @@
         <v>46164</v>
       </c>
       <c r="F13" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:6">
@@ -1321,7 +1321,7 @@
         <v>46164</v>
       </c>
       <c r="F14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1"/>
@@ -1339,7 +1339,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1351,7 +1351,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/my_stocks.xlsx
+++ b/my_stocks.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>stocks</t>
   </si>
@@ -86,6 +86,12 @@
   </si>
   <si>
     <t>神农股份</t>
+  </si>
+  <si>
+    <t>中际旭创</t>
+  </si>
+  <si>
+    <t>上纬新材</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1087,7 @@
         <v>46164</v>
       </c>
       <c r="F2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6">
@@ -1324,8 +1330,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1"/>
-    <row r="16" ht="18" customHeight="1"/>
+    <row r="15" ht="18" customHeight="1" spans="1:6">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="3">
+        <v>43831</v>
+      </c>
+      <c r="C15" s="3">
+        <v>46164</v>
+      </c>
+      <c r="D15" s="3">
+        <v>45292</v>
+      </c>
+      <c r="E15" s="3">
+        <v>46164</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:6">
+      <c r="A16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="3">
+        <v>43831</v>
+      </c>
+      <c r="C16" s="3">
+        <v>46164</v>
+      </c>
+      <c r="D16" s="3">
+        <v>45292</v>
+      </c>
+      <c r="E16" s="3">
+        <v>46164</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+    </row>
     <row r="17" ht="18" customHeight="1"/>
     <row r="18" ht="18" customHeight="1"/>
   </sheetData>

--- a/my_stocks.xlsx
+++ b/my_stocks.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>stocks</t>
   </si>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>中际旭创</t>
-  </si>
-  <si>
-    <t>上纬新材</t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1084,7 @@
         <v>46164</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6">
@@ -1351,24 +1348,10 @@
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:6">
-      <c r="A16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="3">
-        <v>43831</v>
-      </c>
-      <c r="C16" s="3">
-        <v>46164</v>
-      </c>
-      <c r="D16" s="3">
-        <v>45292</v>
-      </c>
-      <c r="E16" s="3">
-        <v>46164</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1</v>
-      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
     </row>
     <row r="17" ht="18" customHeight="1"/>
     <row r="18" ht="18" customHeight="1"/>

--- a/my_stocks.xlsx
+++ b/my_stocks.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32065" windowHeight="14605"/>
+    <workbookView windowWidth="23040" windowHeight="10575"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1037,13 +1037,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="26.954954954955" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7387387387387" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.2252252252252" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.8558558558559" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.9557522123894" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7345132743363" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3362831858407" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.2212389380531" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.858407079646" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1078,13 +1078,13 @@
         <v>46164</v>
       </c>
       <c r="D2" s="3">
-        <v>45292</v>
+        <v>43831</v>
       </c>
       <c r="E2" s="3">
         <v>46164</v>
       </c>
       <c r="F2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6">
@@ -1092,19 +1092,19 @@
         <v>7</v>
       </c>
       <c r="B3" s="3">
-        <v>43831</v>
+        <v>42005</v>
       </c>
       <c r="C3" s="3">
         <v>46164</v>
       </c>
       <c r="D3" s="3">
-        <v>45292</v>
+        <v>42005</v>
       </c>
       <c r="E3" s="3">
         <v>46164</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6">
@@ -1366,7 +1366,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1378,7 +1378,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/my_stocks.xlsx
+++ b/my_stocks.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10575"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1039,11 +1039,11 @@
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="26.9557522123894" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7345132743363" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.3362831858407" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.2212389380531" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.858407079646" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.9583333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.225" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.8583333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1075,16 +1075,16 @@
         <v>43831</v>
       </c>
       <c r="C2" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D2" s="3">
         <v>43831</v>
       </c>
       <c r="E2" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6">
@@ -1092,19 +1092,19 @@
         <v>7</v>
       </c>
       <c r="B3" s="3">
-        <v>42005</v>
+        <v>43831</v>
       </c>
       <c r="C3" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D3" s="3">
-        <v>42005</v>
+        <v>43831</v>
       </c>
       <c r="E3" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6">
@@ -1115,13 +1115,13 @@
         <v>43831</v>
       </c>
       <c r="C4" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D4" s="3">
         <v>45292</v>
       </c>
       <c r="E4" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         <v>43831</v>
       </c>
       <c r="C5" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D5" s="3">
         <v>45292</v>
       </c>
       <c r="E5" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1155,13 +1155,13 @@
         <v>43831</v>
       </c>
       <c r="C6" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D6" s="3">
         <v>45292</v>
       </c>
       <c r="E6" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1175,13 +1175,13 @@
         <v>43831</v>
       </c>
       <c r="C7" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D7" s="3">
         <v>45292</v>
       </c>
       <c r="E7" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -1195,13 +1195,13 @@
         <v>43831</v>
       </c>
       <c r="C8" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D8" s="3">
         <v>45292</v>
       </c>
       <c r="E8" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1215,13 +1215,13 @@
         <v>43831</v>
       </c>
       <c r="C9" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D9" s="3">
         <v>45292</v>
       </c>
       <c r="E9" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1235,13 +1235,13 @@
         <v>43831</v>
       </c>
       <c r="C10" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D10" s="3">
         <v>45292</v>
       </c>
       <c r="E10" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -1255,13 +1255,13 @@
         <v>43831</v>
       </c>
       <c r="C11" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D11" s="3">
         <v>45292</v>
       </c>
       <c r="E11" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -1275,13 +1275,13 @@
         <v>43831</v>
       </c>
       <c r="C12" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D12" s="3">
         <v>45292</v>
       </c>
       <c r="E12" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1295,13 +1295,13 @@
         <v>43831</v>
       </c>
       <c r="C13" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D13" s="3">
         <v>45292</v>
       </c>
       <c r="E13" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -1315,13 +1315,13 @@
         <v>43831</v>
       </c>
       <c r="C14" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D14" s="3">
         <v>45292</v>
       </c>
       <c r="E14" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1335,13 +1335,13 @@
         <v>43831</v>
       </c>
       <c r="C15" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="D15" s="3">
         <v>45292</v>
       </c>
       <c r="E15" s="3">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>

--- a/my_stocks.xlsx
+++ b/my_stocks.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="23040" windowHeight="10575"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>stocks</t>
   </si>
@@ -58,37 +58,16 @@
     <t>云天化</t>
   </si>
   <si>
-    <t>珀莱雅</t>
-  </si>
-  <si>
     <t>紫金矿业</t>
   </si>
   <si>
-    <t>台基股份</t>
+    <t>淮北矿业</t>
   </si>
   <si>
-    <t>深圳华强</t>
+    <t>潞安环能</t>
   </si>
   <si>
-    <t>兆易创新</t>
-  </si>
-  <si>
-    <t>沪电股份</t>
-  </si>
-  <si>
-    <t>立讯精密</t>
-  </si>
-  <si>
-    <t>长电科技</t>
-  </si>
-  <si>
-    <t>赛轮轮胎</t>
-  </si>
-  <si>
-    <t>神农股份</t>
-  </si>
-  <si>
-    <t>中际旭创</t>
+    <t>山西焦煤</t>
   </si>
 </sst>
 </file>
@@ -1036,14 +1015,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="26.9583333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.225" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.8583333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.9557522123894" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7345132743363" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3362831858407" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.2212389380531" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.858407079646" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1075,13 +1054,13 @@
         <v>43831</v>
       </c>
       <c r="C2" s="3">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D2" s="3">
         <v>43831</v>
       </c>
       <c r="E2" s="3">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -1095,13 +1074,13 @@
         <v>43831</v>
       </c>
       <c r="C3" s="3">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D3" s="3">
         <v>43831</v>
       </c>
       <c r="E3" s="3">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -1115,19 +1094,19 @@
         <v>43831</v>
       </c>
       <c r="C4" s="3">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D4" s="3">
-        <v>45292</v>
+        <v>43831</v>
       </c>
       <c r="E4" s="3">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="22" customHeight="1" spans="1:6">
+    <row r="5" ht="18" customHeight="1" spans="1:6">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1135,13 +1114,13 @@
         <v>43831</v>
       </c>
       <c r="C5" s="3">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D5" s="3">
-        <v>45292</v>
+        <v>43831</v>
       </c>
       <c r="E5" s="3">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1155,19 +1134,19 @@
         <v>43831</v>
       </c>
       <c r="C6" s="3">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D6" s="3">
-        <v>45292</v>
+        <v>43831</v>
       </c>
       <c r="E6" s="3">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1" spans="1:6">
+    <row r="7" ht="22" customHeight="1" spans="1:6">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -1175,13 +1154,13 @@
         <v>43831</v>
       </c>
       <c r="C7" s="3">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D7" s="3">
-        <v>45292</v>
+        <v>43831</v>
       </c>
       <c r="E7" s="3">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -1195,166 +1174,19 @@
         <v>43831</v>
       </c>
       <c r="C8" s="3">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="D8" s="3">
-        <v>45292</v>
+        <v>43831</v>
       </c>
       <c r="E8" s="3">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="3">
-        <v>43831</v>
-      </c>
-      <c r="C9" s="3">
-        <v>46167</v>
-      </c>
-      <c r="D9" s="3">
-        <v>45292</v>
-      </c>
-      <c r="E9" s="3">
-        <v>46167</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="3">
-        <v>43831</v>
-      </c>
-      <c r="C10" s="3">
-        <v>46167</v>
-      </c>
-      <c r="D10" s="3">
-        <v>45292</v>
-      </c>
-      <c r="E10" s="3">
-        <v>46167</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="3">
-        <v>43831</v>
-      </c>
-      <c r="C11" s="3">
-        <v>46167</v>
-      </c>
-      <c r="D11" s="3">
-        <v>45292</v>
-      </c>
-      <c r="E11" s="3">
-        <v>46167</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:6">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="3">
-        <v>43831</v>
-      </c>
-      <c r="C12" s="3">
-        <v>46167</v>
-      </c>
-      <c r="D12" s="3">
-        <v>45292</v>
-      </c>
-      <c r="E12" s="3">
-        <v>46167</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:6">
-      <c r="A13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="3">
-        <v>43831</v>
-      </c>
-      <c r="C13" s="3">
-        <v>46167</v>
-      </c>
-      <c r="D13" s="3">
-        <v>45292</v>
-      </c>
-      <c r="E13" s="3">
-        <v>46167</v>
-      </c>
-      <c r="F13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:6">
-      <c r="A14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="3">
-        <v>43831</v>
-      </c>
-      <c r="C14" s="3">
-        <v>46167</v>
-      </c>
-      <c r="D14" s="3">
-        <v>45292</v>
-      </c>
-      <c r="E14" s="3">
-        <v>46167</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:6">
-      <c r="A15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="3">
-        <v>43831</v>
-      </c>
-      <c r="C15" s="3">
-        <v>46167</v>
-      </c>
-      <c r="D15" s="3">
-        <v>45292</v>
-      </c>
-      <c r="E15" s="3">
-        <v>46167</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:6">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-    </row>
-    <row r="17" ht="18" customHeight="1"/>
-    <row r="18" ht="18" customHeight="1"/>
+    <row r="9" ht="18" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/my_stocks.xlsx
+++ b/my_stocks.xlsx
@@ -1143,7 +1143,7 @@
         <v>46168</v>
       </c>
       <c r="F6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6">

--- a/my_stocks.xlsx
+++ b/my_stocks.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10575"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,13 +61,13 @@
     <t>紫金矿业</t>
   </si>
   <si>
-    <t>淮北矿业</t>
+    <t>陕西煤业</t>
   </si>
   <si>
-    <t>潞安环能</t>
+    <t>华能蒙电</t>
   </si>
   <si>
-    <t>山西焦煤</t>
+    <t>长江电力</t>
   </si>
 </sst>
 </file>
@@ -1018,11 +1018,11 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="26.9557522123894" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7345132743363" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.3362831858407" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.2212389380531" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.858407079646" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.9583333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.225" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.8583333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1063,7 +1063,7 @@
         <v>46168</v>
       </c>
       <c r="F2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6">
@@ -1163,7 +1163,7 @@
         <v>46168</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:6">

--- a/my_stocks.xlsx
+++ b/my_stocks.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="23040" windowHeight="10575"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1018,11 +1018,11 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="26.9583333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7333333333333" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.3333333333333" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.225" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.8583333333333" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.9557522123894" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7345132743363" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3362831858407" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.2212389380531" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.858407079646" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1063,7 +1063,7 @@
         <v>46168</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6">
@@ -1163,7 +1163,7 @@
         <v>46168</v>
       </c>
       <c r="F7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:6">

--- a/my_stocks.xlsx
+++ b/my_stocks.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="10575"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1015,14 +1015,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="26.9557522123894" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7345132743363" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.3362831858407" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.2212389380531" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.858407079646" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.9583333333333" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7333333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.225" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.8583333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1051,19 +1051,19 @@
         <v>6</v>
       </c>
       <c r="B2" s="3">
-        <v>43831</v>
+        <v>43466</v>
       </c>
       <c r="C2" s="3">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="D2" s="3">
-        <v>43831</v>
+        <v>43466</v>
       </c>
       <c r="E2" s="3">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6">
@@ -1071,19 +1071,19 @@
         <v>7</v>
       </c>
       <c r="B3" s="3">
-        <v>43831</v>
+        <v>43466</v>
       </c>
       <c r="C3" s="3">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="D3" s="3">
-        <v>43831</v>
+        <v>43466</v>
       </c>
       <c r="E3" s="3">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F3" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6">
@@ -1091,16 +1091,16 @@
         <v>8</v>
       </c>
       <c r="B4" s="3">
-        <v>43831</v>
+        <v>43466</v>
       </c>
       <c r="C4" s="3">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="D4" s="3">
-        <v>43831</v>
+        <v>43466</v>
       </c>
       <c r="E4" s="3">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1111,16 +1111,16 @@
         <v>9</v>
       </c>
       <c r="B5" s="3">
-        <v>43831</v>
+        <v>43466</v>
       </c>
       <c r="C5" s="3">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="D5" s="3">
-        <v>43831</v>
+        <v>43466</v>
       </c>
       <c r="E5" s="3">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -1131,16 +1131,16 @@
         <v>10</v>
       </c>
       <c r="B6" s="3">
-        <v>43831</v>
+        <v>43466</v>
       </c>
       <c r="C6" s="3">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="D6" s="3">
-        <v>43831</v>
+        <v>43466</v>
       </c>
       <c r="E6" s="3">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1151,16 +1151,16 @@
         <v>11</v>
       </c>
       <c r="B7" s="3">
-        <v>43831</v>
+        <v>43466</v>
       </c>
       <c r="C7" s="3">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="D7" s="3">
-        <v>43831</v>
+        <v>43466</v>
       </c>
       <c r="E7" s="3">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -1171,22 +1171,21 @@
         <v>12</v>
       </c>
       <c r="B8" s="3">
-        <v>43831</v>
+        <v>43466</v>
       </c>
       <c r="C8" s="3">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="D8" s="3">
-        <v>43831</v>
+        <v>43466</v>
       </c>
       <c r="E8" s="3">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/my_stocks.xlsx
+++ b/my_stocks.xlsx
@@ -1051,19 +1051,19 @@
         <v>6</v>
       </c>
       <c r="B2" s="3">
-        <v>43466</v>
+        <v>44197</v>
       </c>
       <c r="C2" s="3">
         <v>46169</v>
       </c>
       <c r="D2" s="3">
-        <v>43466</v>
+        <v>44197</v>
       </c>
       <c r="E2" s="3">
         <v>46169</v>
       </c>
       <c r="F2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6">
@@ -1071,13 +1071,13 @@
         <v>7</v>
       </c>
       <c r="B3" s="3">
-        <v>43466</v>
+        <v>44197</v>
       </c>
       <c r="C3" s="3">
         <v>46169</v>
       </c>
       <c r="D3" s="3">
-        <v>43466</v>
+        <v>44197</v>
       </c>
       <c r="E3" s="3">
         <v>46169</v>
@@ -1091,19 +1091,19 @@
         <v>8</v>
       </c>
       <c r="B4" s="3">
-        <v>43466</v>
+        <v>44197</v>
       </c>
       <c r="C4" s="3">
         <v>46169</v>
       </c>
       <c r="D4" s="3">
-        <v>43466</v>
+        <v>44197</v>
       </c>
       <c r="E4" s="3">
         <v>46169</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:6">
@@ -1111,19 +1111,19 @@
         <v>9</v>
       </c>
       <c r="B5" s="3">
-        <v>43466</v>
+        <v>44197</v>
       </c>
       <c r="C5" s="3">
         <v>46169</v>
       </c>
       <c r="D5" s="3">
-        <v>43466</v>
+        <v>44197</v>
       </c>
       <c r="E5" s="3">
         <v>46169</v>
       </c>
       <c r="F5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:6">
@@ -1131,13 +1131,13 @@
         <v>10</v>
       </c>
       <c r="B6" s="3">
-        <v>43466</v>
+        <v>44197</v>
       </c>
       <c r="C6" s="3">
         <v>46169</v>
       </c>
       <c r="D6" s="3">
-        <v>43466</v>
+        <v>44197</v>
       </c>
       <c r="E6" s="3">
         <v>46169</v>
@@ -1151,13 +1151,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="3">
-        <v>43466</v>
+        <v>44197</v>
       </c>
       <c r="C7" s="3">
         <v>46169</v>
       </c>
       <c r="D7" s="3">
-        <v>43466</v>
+        <v>44197</v>
       </c>
       <c r="E7" s="3">
         <v>46169</v>
@@ -1171,13 +1171,13 @@
         <v>12</v>
       </c>
       <c r="B8" s="3">
-        <v>43466</v>
+        <v>44197</v>
       </c>
       <c r="C8" s="3">
         <v>46169</v>
       </c>
       <c r="D8" s="3">
-        <v>43466</v>
+        <v>44197</v>
       </c>
       <c r="E8" s="3">
         <v>46169</v>

--- a/my_stocks.xlsx
+++ b/my_stocks.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>stocks</t>
   </si>
@@ -68,6 +68,12 @@
   </si>
   <si>
     <t>长江电力</t>
+  </si>
+  <si>
+    <t>赣锋锂业</t>
+  </si>
+  <si>
+    <t>北方稀土</t>
   </si>
 </sst>
 </file>
@@ -1015,8 +1021,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="26.9583333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="16.7333333333333" style="1" customWidth="1"/>
@@ -1054,13 +1060,13 @@
         <v>44197</v>
       </c>
       <c r="C2" s="3">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D2" s="3">
         <v>44197</v>
       </c>
       <c r="E2" s="3">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -1074,16 +1080,16 @@
         <v>44197</v>
       </c>
       <c r="C3" s="3">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D3" s="3">
         <v>44197</v>
       </c>
       <c r="E3" s="3">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6">
@@ -1094,16 +1100,16 @@
         <v>44197</v>
       </c>
       <c r="C4" s="3">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D4" s="3">
         <v>44197</v>
       </c>
       <c r="E4" s="3">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F4" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:6">
@@ -1114,16 +1120,16 @@
         <v>44197</v>
       </c>
       <c r="C5" s="3">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D5" s="3">
         <v>44197</v>
       </c>
       <c r="E5" s="3">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:6">
@@ -1134,13 +1140,13 @@
         <v>44197</v>
       </c>
       <c r="C6" s="3">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D6" s="3">
         <v>44197</v>
       </c>
       <c r="E6" s="3">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1154,13 +1160,13 @@
         <v>44197</v>
       </c>
       <c r="C7" s="3">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D7" s="3">
         <v>44197</v>
       </c>
       <c r="E7" s="3">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -1174,15 +1180,55 @@
         <v>44197</v>
       </c>
       <c r="C8" s="3">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="D8" s="3">
         <v>44197</v>
       </c>
       <c r="E8" s="3">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="F8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3">
+        <v>44197</v>
+      </c>
+      <c r="C9" s="3">
+        <v>46171</v>
+      </c>
+      <c r="D9" s="3">
+        <v>44197</v>
+      </c>
+      <c r="E9" s="3">
+        <v>46171</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3">
+        <v>44197</v>
+      </c>
+      <c r="C10" s="3">
+        <v>46171</v>
+      </c>
+      <c r="D10" s="3">
+        <v>44197</v>
+      </c>
+      <c r="E10" s="3">
+        <v>46171</v>
+      </c>
+      <c r="F10" s="1">
         <v>0</v>
       </c>
     </row>
